--- a/docs/templates/company_detector_sales_sheet_template.xlsx
+++ b/docs/templates/company_detector_sales_sheet_template.xlsx
@@ -410,11 +410,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:Q200"/>
   <mergeCells count="2">
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
   </mergeCells>
-  <autoFilter ref="A4:Q200"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B5:B500">
       <formula1>'Options'!$A$2:$A$3</formula1>

--- a/docs/templates/company_detector_sales_sheet_template.xlsx
+++ b/docs/templates/company_detector_sales_sheet_template.xlsx
@@ -354,7 +354,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="74" customHeight="1">
       <c r="A6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">21 Mei 2026, 09:00 WIB</t>
@@ -392,9 +392,23 @@
       </c>
       <c r="H6" s="0"/>
       <c r="I6" s="0"/>
-      <c r="J6" s="0"/>
-      <c r="K6" s="0"/>
-      <c r="L6" s="0"/>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokopedia: https://www.tokopedia.com/falasik</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Instagram: https://instagram.com/falasik
+TikTok: https://tiktok.com/@falasik
+LinkedIn: https://au.linkedin.com/in/falasik</t>
+        </is>
+      </c>
+      <c r="L6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://falasik.com</t>
+        </is>
+      </c>
       <c r="M6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Register platform</t>
